--- a/public/template_officer.xlsx
+++ b/public/template_officer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\iocl_utility_app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F7E028-9A28-42A7-81FB-96D946F4E94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF06B6D-A3E9-4813-96FD-0023B18BC001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="4695" windowWidth="21600" windowHeight="12585" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>LOCATION CODE</t>
   </si>
@@ -53,10 +53,13 @@
     <t>MAIL ID</t>
   </si>
   <si>
-    <t>OFFICER NAME</t>
+    <t>ROLE</t>
   </si>
   <si>
-    <t>ROLE</t>
+    <t>EMPLOYEE ID</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
 </sst>
 </file>
@@ -458,80 +461,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B31A7F-BFB1-41BA-B4C8-1FAA0EA5DE74}">
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="3" width="14.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -1184,8 +1191,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{9A491BDF-DFEE-4A14-8E1B-7606A0985EA4}">
-      <formula1>"SECURITY,ADMIN,SUPER_ADMIN"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{9A491BDF-DFEE-4A14-8E1B-7606A0985EA4}">
+      <formula1>"SECURITY,ADMIN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/template_officer.xlsx
+++ b/public/template_officer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\iocl_utility_app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF06B6D-A3E9-4813-96FD-0023B18BC001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4062C1D5-4331-49D1-B2F7-715F5927CE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>LOCATION CODE</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>NAME</t>
+  </si>
+  <si>
+    <t>DESIGNATION</t>
   </si>
 </sst>
 </file>
@@ -109,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -125,6 +128,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -461,84 +470,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B31A7F-BFB1-41BA-B4C8-1FAA0EA5DE74}">
-  <dimension ref="A1:I232"/>
+  <dimension ref="A1:J232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="3" width="14.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -1191,7 +1204,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{9A491BDF-DFEE-4A14-8E1B-7606A0985EA4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{9A491BDF-DFEE-4A14-8E1B-7606A0985EA4}">
       <formula1>"SECURITY,ADMIN"</formula1>
     </dataValidation>
   </dataValidations>
